--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.95395757762606</v>
+        <v>3.242518106364234</v>
       </c>
       <c r="D2" t="n">
-        <v>17.76770679351237</v>
+        <v>2.88725235394576</v>
       </c>
       <c r="E2" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F2" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.91753649780761</v>
+        <v>4.374099680893736</v>
       </c>
       <c r="D3" t="n">
-        <v>24.37078917814895</v>
+        <v>3.960253241449204</v>
       </c>
       <c r="E3" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F3" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.68465712493998</v>
+        <v>3.036256782802746</v>
       </c>
       <c r="D4" t="n">
-        <v>15.46443253344954</v>
+        <v>2.512970286685551</v>
       </c>
       <c r="E4" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F4" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.16375243335455</v>
+        <v>6.526609770420115</v>
       </c>
       <c r="D5" t="n">
-        <v>40.40876355555571</v>
+        <v>6.566424077777802</v>
       </c>
       <c r="E5" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F5" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.19206975289912</v>
+        <v>8.806211334846106</v>
       </c>
       <c r="D6" t="n">
-        <v>54.55637580005516</v>
+        <v>8.865411067508964</v>
       </c>
       <c r="E6" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F6" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.79779428315154</v>
+        <v>9.717141571012126</v>
       </c>
       <c r="D7" t="n">
-        <v>63.81086468703949</v>
+        <v>10.36926551164392</v>
       </c>
       <c r="E7" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F7" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18298666603025</v>
+        <v>11.40473533322992</v>
       </c>
       <c r="D8" t="n">
-        <v>74.02923286647047</v>
+        <v>12.02975034080145</v>
       </c>
       <c r="E8" t="n">
-        <v>18.96524855799171</v>
+        <v>3.081852890673654</v>
       </c>
       <c r="F8" t="n">
-        <v>21.587253490028</v>
+        <v>3.507928692129549</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
